--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>779.7911421967376</v>
+        <v>768.7737844609022</v>
       </c>
       <c r="Q7" s="45">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.07114987812794116</v>
+        <v>0.07180269336360408</v>
       </c>
       <c r="Q14" s="29">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>768.7737844609022</v>
+        <v>770.5522798289841</v>
       </c>
       <c r="Q7" s="45">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.07180269336360408</v>
+        <v>0.06867752809326033</v>
       </c>
       <c r="Q14" s="29">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>770.5522798289841</v>
+        <v>744.2308673737426</v>
       </c>
       <c r="Q7" s="45">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06867752809326033</v>
+        <v>0.06486465391208283</v>
       </c>
       <c r="Q14" s="29">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>744.2308673737426</v>
+        <v>748.2074145238203</v>
       </c>
       <c r="Q7" s="45">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06486465391208283</v>
+        <v>0.06904143586972294</v>
       </c>
       <c r="Q14" s="29">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>748.2074145238203</v>
+        <v>747.5726309067816</v>
       </c>
       <c r="Q7" s="45">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06904143586972294</v>
+        <v>0.06761602879313641</v>
       </c>
       <c r="Q14" s="29">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>747.5726309067816</v>
+        <v>754.6195529803811</v>
       </c>
       <c r="Q7" s="45">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06761602879313641</v>
+        <v>0.06712599508648684</v>
       </c>
       <c r="Q14" s="29">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>754.6195529803811</v>
+        <v>746.3521546806509</v>
       </c>
       <c r="Q7" s="45">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06712599508648684</v>
+        <v>0.06493064590380496</v>
       </c>
       <c r="Q14" s="29">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>746.3521546806509</v>
+        <v>743.3311450736135</v>
       </c>
       <c r="Q7" s="45">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06493064590380496</v>
+        <v>0.0631159484104428</v>
       </c>
       <c r="Q14" s="29">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>743.3311450736135</v>
+        <v>713.8517466446867</v>
       </c>
       <c r="Q7" s="45">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.0631159484104428</v>
+        <v>0.05655663620885869</v>
       </c>
       <c r="Q14" s="29">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>713.8517466446867</v>
+        <v>730.6656791408525</v>
       </c>
       <c r="Q7" s="45">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05655663620885869</v>
+        <v>0.06002822455536317</v>
       </c>
       <c r="Q14" s="29">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>730.6656791408525</v>
+        <v>722.1160555101192</v>
       </c>
       <c r="Q7" s="45">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06002822455536317</v>
+        <v>0.06129017080883686</v>
       </c>
       <c r="Q14" s="29">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>722.1160555101192</v>
+        <v>720.0357916039862</v>
       </c>
       <c r="Q7" s="45">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06129017080883686</v>
+        <v>0.05896506615341346</v>
       </c>
       <c r="Q14" s="29">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>720.0357916039862</v>
+        <v>726.9104878324572</v>
       </c>
       <c r="Q7" s="45">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05896506615341346</v>
+        <v>0.05853569209247313</v>
       </c>
       <c r="Q14" s="29">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>726.9104878324572</v>
+        <v>729.0926522303906</v>
       </c>
       <c r="Q7" s="45">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05853569209247313</v>
+        <v>0.056080509025841586</v>
       </c>
       <c r="Q14" s="29">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>729.0926522303906</v>
+        <v>743.7234818798476</v>
       </c>
       <c r="Q7" s="45">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.056080509025841586</v>
+        <v>0.060148276265888354</v>
       </c>
       <c r="Q14" s="29">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>743.7234818798476</v>
+        <v>740.0576426555651</v>
       </c>
       <c r="Q7" s="45">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.060148276265888354</v>
+        <v>0.060093469167183715</v>
       </c>
       <c r="Q14" s="29">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>740.0576426555651</v>
+        <v>742.1813208707022</v>
       </c>
       <c r="Q7" s="45">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.060093469167183715</v>
+        <v>0.061648375192475964</v>
       </c>
       <c r="Q14" s="29">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>742.1813208707022</v>
+        <v>738.1858436309551</v>
       </c>
       <c r="Q7" s="45">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.061648375192475964</v>
+        <v>0.06034142796802716</v>
       </c>
       <c r="Q14" s="29">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>738.1858436309551</v>
+        <v>745.0378684378305</v>
       </c>
       <c r="Q7" s="45">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06034142796802716</v>
+        <v>0.05927333835776991</v>
       </c>
       <c r="Q14" s="29">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>745.0378684378305</v>
+        <v>738.6100965627659</v>
       </c>
       <c r="Q7" s="45">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05927333835776991</v>
+        <v>0.056860959623755446</v>
       </c>
       <c r="Q14" s="29">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>738.6100965627659</v>
+        <v>735.9651538288232</v>
       </c>
       <c r="Q7" s="45">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.056860959623755446</v>
+        <v>0.05748416652063985</v>
       </c>
       <c r="Q14" s="29">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>735.9651538288232</v>
+        <v>744.5073347344307</v>
       </c>
       <c r="Q7" s="45">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05748416652063985</v>
+        <v>0.06192996983201851</v>
       </c>
       <c r="Q14" s="29">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>744.5073347344307</v>
+        <v>751.7140377413642</v>
       </c>
       <c r="Q7" s="45">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.06192996983201851</v>
+        <v>0.05971728512838891</v>
       </c>
       <c r="Q14" s="29">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>751.7140377413642</v>
+        <v>713.8537509436683</v>
       </c>
       <c r="Q7" s="45">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05971728512838891</v>
+        <v>0.05528243966029945</v>
       </c>
       <c r="Q14" s="29">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>

--- a/excel/latest/Flap_MYX_控筹模型.xlsx
+++ b/excel/latest/Flap_MYX_控筹模型.xlsx
@@ -5031,10 +5031,10 @@
       <c r="N7" s="35"/>
       <c r="O7" s="35"/>
       <c r="P7" s="44">
-        <v>713.8537509436683</v>
+        <v>701.7319115078789</v>
       </c>
       <c r="Q7" s="45">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="R7" s="35" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         <v>2026-10-07</v>
       </c>
       <c r="P14" s="150">
-        <v>0.05528243966029945</v>
+        <v>0.05544919109073895</v>
       </c>
       <c r="Q14" s="29">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
